--- a/artfynd/A 48449-2021 artfynd.xlsx
+++ b/artfynd/A 48449-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>121344501</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 48449-2021 artfynd.xlsx
+++ b/artfynd/A 48449-2021 artfynd.xlsx
@@ -925,7 +925,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Grim Skog, Uno Skog</t>
+          <t>Uno Skog, Grim Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 48449-2021 artfynd.xlsx
+++ b/artfynd/A 48449-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>121344501</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Skog, Grim Skog</t>
+          <t>Grim Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 48449-2021 artfynd.xlsx
+++ b/artfynd/A 48449-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>121344501</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Grim Skog, Uno Skog</t>
+          <t>Uno Skog, Grim Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 48449-2021 artfynd.xlsx
+++ b/artfynd/A 48449-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>121344501</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Skog, Grim Skog</t>
+          <t>Grim Skog, Uno Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 48449-2021 artfynd.xlsx
+++ b/artfynd/A 48449-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>121344501</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 48449-2021 artfynd.xlsx
+++ b/artfynd/A 48449-2021 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>121344501</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 48449-2021 artfynd.xlsx
+++ b/artfynd/A 48449-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119005114</v>
+        <v>102724423</v>
       </c>
       <c r="B2" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4379</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rinnen, Vrm</t>
+          <t>Vindlestan, Smolmark, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>340813</v>
+        <v>340768</v>
       </c>
       <c r="R2" t="n">
-        <v>6604629</v>
+        <v>6604690</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Drygt 40 blomstänglar I 5 grupper inom 20 meter.</t>
+          <t>Intill nordöstra stugknuten, vid stuprörets utlopp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,71 +790,63 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Uno Skog, Grim Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121344501</v>
+        <v>57827884</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rinnen, N om, Vrm</t>
+          <t>Vindlestan Rinnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>340812</v>
+        <v>340777</v>
       </c>
       <c r="R3" t="n">
-        <v>6604629</v>
+        <v>6604707</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,24 +871,29 @@
           <t>Karlanda</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>S-Årj-0401</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2016-03-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2016-03-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Drygt 40 blomstänglar I 5 grupper inom 20 meter.Även rapporterad från RT90: 6608817 - 1295233, 12 ex.</t>
+          <t>Två spillkråkor som ropade på var sida om sjön, den väst om sjön trummade också.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,15 +908,2837 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111304435</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Smolmark Vindelstan, Smolmark Vindelstan, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>340765</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6604694</v>
+      </c>
+      <c r="S4" t="n">
+        <v>16</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>57828010</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vindlestan Rinnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>340777</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6604707</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-03-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-03-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118987558</v>
+      </c>
+      <c r="B6" t="n">
+        <v>41271</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100230</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skägglavmätare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alcis jubata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Thunberg, 1788)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vindlestan, Smolmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>340768</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6604690</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>00:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>00:31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>57889663</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vindlestan Rinnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>340777</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6604707</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-03-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-03-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>57903482</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vindlestan Rinnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>340777</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6604707</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-03-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-03-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Orrspel hördes SV om Rinnen.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128736597</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Smolmark Vindelstan, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>340770</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6604703</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog, Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>57827820</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vindlestan Rinnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>340777</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6604707</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-03-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-03-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110301364</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Smolmark Vindelstan, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>340770</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6604703</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131996692</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vindlestan, Smolmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>340768</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6604690</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110304075</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Smolmark Vindelstan, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>340777</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6604698</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>57827836</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vindlestan Rinnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>340777</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6604707</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2016-03-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2016-03-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>110302907</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vindlestan, Smolmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>340776</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6604684</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>21:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Uno Skog, Freja Skog</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>94831972</v>
+      </c>
+      <c r="B16" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Smolmark Vindelstan, Smolmark Vindelstan, Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>340778</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6604695</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>57903524</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vindlestan Rinnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>340777</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6604707</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2016-03-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2016-03-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hördes från V sidan Rinnen.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110323858</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vindlestan, Smolmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>340776</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6604684</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sprang fram och tillbaka mellan Jonas stuga och vår stuga.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Uno Skog, Freja Skog, Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>102724503</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vindlestan, Smolmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>340771</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6604700</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>110327206</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Smolmark Vindelstan, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>340757</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6604690</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>111238227</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rinnen, Smolmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>340791</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6604584</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126798148</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vindlestan, Smolmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>340812</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6604717</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>102727248</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vindlestan, Smolmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>340771</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6604700</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>111284803</v>
+      </c>
+      <c r="B24" t="n">
+        <v>42865</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>216248</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Baltiskt skogsfly</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Xestia baltica</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Valle, 1940)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vindlestan, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>340872</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6604656</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-08-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-08-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>I granskog med blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>119005000</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rinnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>340800</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6604595</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Uno Skog, Grim Skog</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>119005114</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rinnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>340813</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6604629</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Drygt 40 blomstänglar I 5 grupper inom 20 meter.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Uno Skog, Grim Skog</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121344501</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Rinnen, N om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>340812</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6604629</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>S-Årj-0401</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Drygt 40 blomstänglar I 5 grupper inom 20 meter.Även rapporterad från RT90: 6608817 - 1295233, 12 ex.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Grim Skog, Uno Skog</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 48449-2021 artfynd.xlsx
+++ b/artfynd/A 48449-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1970,10 +1970,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110304075</v>
+        <v>134505921</v>
       </c>
       <c r="B13" t="n">
-        <v>58439</v>
+        <v>58349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,43 +1981,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Smolmark Vindelstan, Vrm</t>
+          <t>Rinnen, Smolmark, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>340777</v>
+        <v>340768</v>
       </c>
       <c r="R13" t="n">
-        <v>6604698</v>
+        <v>6604639</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2041,12 +2044,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>21:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,22 +2074,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>57827836</v>
+        <v>110304075</v>
       </c>
       <c r="B14" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,41 +2097,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vindlestan Rinnen, Vrm</t>
+          <t>Smolmark Vindelstan, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>340777</v>
       </c>
       <c r="R14" t="n">
-        <v>6604707</v>
+        <v>6604698</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2145,22 +2157,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2016-03-26</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2016-03-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>08:15</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,10 +2189,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110302907</v>
+        <v>134503577</v>
       </c>
       <c r="B15" t="n">
-        <v>58636</v>
+        <v>58461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,32 +2200,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2232,13 +2238,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>340776</v>
+        <v>340768</v>
       </c>
       <c r="R15" t="n">
-        <v>6604684</v>
+        <v>6604690</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2262,22 +2268,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,34 +2303,34 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Uno Skog, Freja Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>94831972</v>
+        <v>57827836</v>
       </c>
       <c r="B16" t="n">
-        <v>43258</v>
+        <v>58636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>201129</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2332,37 +2338,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Smolmark Vindelstan, Smolmark Vindelstan, Årjäng, Vrm</t>
+          <t>Vindlestan Rinnen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>340778</v>
+        <v>340777</v>
       </c>
       <c r="R16" t="n">
-        <v>6604695</v>
+        <v>6604707</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2389,22 +2382,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2016-03-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2016-03-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>57903524</v>
+        <v>110302907</v>
       </c>
       <c r="B17" t="n">
-        <v>58085</v>
+        <v>58636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,21 +2435,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205976</v>
+        <v>103044</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2465,7 +2458,6 @@
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -2473,14 +2465,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vindlestan Rinnen, Vrm</t>
+          <t>Vindlestan, Smolmark, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>340777</v>
+        <v>340776</v>
       </c>
       <c r="R17" t="n">
-        <v>6604707</v>
+        <v>6604684</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2507,27 +2499,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-03-31</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-03-31</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hördes från V sidan Rinnen.</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,22 +2529,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog, Freja Skog</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110323858</v>
+        <v>94831972</v>
       </c>
       <c r="B18" t="n">
-        <v>56522</v>
+        <v>43258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,39 +2552,54 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>206004</v>
+        <v>201129</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vindlestan, Smolmark, Vrm</t>
+          <t>Smolmark Vindelstan, Smolmark Vindelstan, Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>340776</v>
+        <v>340778</v>
       </c>
       <c r="R18" t="n">
-        <v>6604684</v>
+        <v>6604695</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2624,27 +2626,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sprang fram och tillbaka mellan Jonas stuga och vår stuga.</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,22 +2656,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Uno Skog, Freja Skog, Sofia Möller Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102724503</v>
+        <v>57903524</v>
       </c>
       <c r="B19" t="n">
-        <v>58790</v>
+        <v>58085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2682,41 +2679,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208245</v>
+        <v>205976</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vindlestan, Smolmark, Vrm</t>
+          <t>Vindlestan Rinnen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>340771</v>
+        <v>340777</v>
       </c>
       <c r="R19" t="n">
-        <v>6604700</v>
+        <v>6604707</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2743,22 +2744,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2016-03-31</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2016-03-31</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hördes från V sidan Rinnen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2773,62 +2779,62 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110327206</v>
+        <v>110323858</v>
       </c>
       <c r="B20" t="n">
-        <v>58790</v>
+        <v>56522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208245</v>
+        <v>206004</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Smolmark Vindelstan, Vrm</t>
+          <t>Vindlestan, Smolmark, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>340757</v>
+        <v>340776</v>
       </c>
       <c r="R20" t="n">
-        <v>6604690</v>
+        <v>6604684</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2855,22 +2861,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>02:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>02:05</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Sprang fram och tillbaka mellan Jonas stuga och vår stuga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2885,19 +2896,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog, Freja Skog, Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111238227</v>
+        <v>102724503</v>
       </c>
       <c r="B21" t="n">
         <v>58790</v>
@@ -2925,25 +2936,27 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rinnen, Smolmark, Vrm</t>
+          <t>Vindlestan, Smolmark, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>340791</v>
+        <v>340771</v>
       </c>
       <c r="R21" t="n">
-        <v>6604584</v>
+        <v>6604700</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2967,22 +2980,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,7 +3022,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126798148</v>
+        <v>110327206</v>
       </c>
       <c r="B22" t="n">
         <v>58790</v>
@@ -3042,16 +3055,17 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vindlestan, Smolmark, Vrm</t>
+          <t>Smolmark Vindelstan, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>340812</v>
+        <v>340757</v>
       </c>
       <c r="R22" t="n">
-        <v>6604717</v>
+        <v>6604690</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3078,22 +3092,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>02:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2023-06-25</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>02:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3108,22 +3122,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102727248</v>
+        <v>111238227</v>
       </c>
       <c r="B23" t="n">
-        <v>56884</v>
+        <v>58790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3131,21 +3145,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208255</v>
+        <v>208245</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3153,31 +3167,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vindlestan, Smolmark, Vrm</t>
+          <t>Rinnen, Smolmark, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>340771</v>
+        <v>340791</v>
       </c>
       <c r="R23" t="n">
-        <v>6604700</v>
+        <v>6604584</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3201,22 +3204,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,67 +3246,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111284803</v>
+        <v>126798148</v>
       </c>
       <c r="B24" t="n">
-        <v>42865</v>
+        <v>58790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>216248</v>
+        <v>208245</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Baltiskt skogsfly</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Xestia baltica</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Valle, 1940)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>ljusfälla</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vindlestan, Vrm</t>
+          <t>Vindlestan, Smolmark, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>340872</v>
+        <v>340812</v>
       </c>
       <c r="R24" t="n">
-        <v>6604656</v>
+        <v>6604717</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3327,27 +3315,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>I granskog med blåbärsris.</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3374,59 +3357,61 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119005000</v>
+        <v>102727248</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>56884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>208255</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rinnen, Vrm</t>
+          <t>Vindlestan, Smolmark, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>340800</v>
+        <v>340771</v>
       </c>
       <c r="R25" t="n">
-        <v>6604595</v>
+        <v>6604700</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3453,22 +3438,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3488,69 +3473,74 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Uno Skog, Grim Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119005114</v>
+        <v>111284803</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>42865</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>216248</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Baltiskt skogsfly</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Xestia baltica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Valle, 1940)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rinnen, Vrm</t>
+          <t>Vindlestan, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>340813</v>
+        <v>340872</v>
       </c>
       <c r="R26" t="n">
-        <v>6604629</v>
+        <v>6604656</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3574,27 +3564,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Drygt 40 blomstänglar I 5 grupper inom 20 meter.</t>
+          <t>I granskog med blåbärsris.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3614,14 +3604,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Uno Skog, Grim Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121344501</v>
+        <v>119005000</v>
       </c>
       <c r="B27" t="n">
         <v>99118</v>
@@ -3651,7 +3641,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3661,19 +3651,19 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rinnen, N om, Vrm</t>
+          <t>Rinnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>340812</v>
+        <v>340800</v>
       </c>
       <c r="R27" t="n">
-        <v>6604629</v>
+        <v>6604595</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3698,24 +3688,24 @@
           <t>Karlanda</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>S-Årj-0401</t>
-        </is>
-      </c>
       <c r="Y27" t="inlineStr">
         <is>
           <t>2024-08-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-08</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Drygt 40 blomstänglar I 5 grupper inom 20 meter.Även rapporterad från RT90: 6608817 - 1295233, 12 ex.</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3730,15 +3720,262 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Uno Skog, Grim Skog</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>119005114</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Rinnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>340813</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6604629</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Drygt 40 blomstänglar I 5 grupper inom 20 meter.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Uno Skog, Grim Skog</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121344501</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Rinnen, N om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>340812</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6604629</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>S-Årj-0401</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Drygt 40 blomstänglar I 5 grupper inom 20 meter.Även rapporterad från RT90: 6608817 - 1295233, 12 ex.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Grim Skog, Uno Skog</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr">
+      <c r="AY29" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
